--- a/artfynd/A 37027-2023 artfynd.xlsx
+++ b/artfynd/A 37027-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37027-2023 artfynd.xlsx
+++ b/artfynd/A 37027-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111941810</v>
+        <v>111943231</v>
       </c>
       <c r="B2" t="n">
-        <v>86357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4405</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475800</v>
+        <v>476020</v>
       </c>
       <c r="R2" t="n">
-        <v>7057037</v>
+        <v>7056722</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,54 +773,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111942305</v>
+        <v>112818906</v>
       </c>
       <c r="B3" t="n">
-        <v>86305</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3624</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475683</v>
+        <v>476130</v>
       </c>
       <c r="R3" t="n">
-        <v>7057042</v>
+        <v>7057242</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,12 +839,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,54 +871,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111941749</v>
+        <v>112818753</v>
       </c>
       <c r="B4" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1599</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>475800</v>
+        <v>476130</v>
       </c>
       <c r="R4" t="n">
-        <v>7057037</v>
+        <v>7057242</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -952,12 +937,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111942805</v>
+        <v>112819093</v>
       </c>
       <c r="B5" t="n">
-        <v>85476</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,38 +980,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3528</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitterspindling</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius agathosmus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brandrud, H.Lindstr. &amp; Melot</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>475892</v>
+        <v>476050</v>
       </c>
       <c r="R5" t="n">
-        <v>7056961</v>
+        <v>7057224</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1035,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,51 +1067,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111942167</v>
+        <v>111941749</v>
       </c>
       <c r="B6" t="n">
-        <v>85448</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3739</v>
+        <v>1599</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>475832</v>
+        <v>475800</v>
       </c>
       <c r="R6" t="n">
-        <v>7057097</v>
+        <v>7057037</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1193,12 +1168,7 @@
         <v>111941479</v>
       </c>
       <c r="B7" t="n">
-        <v>90799</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,26 +1185,26 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>475758</v>
       </c>
       <c r="R7" t="n">
-        <v>7057000</v>
+        <v>7057001</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1293,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111942683</v>
+        <v>111940665</v>
       </c>
       <c r="B8" t="n">
-        <v>90806</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1309,35 +1274,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>1988</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>475748</v>
+        <v>475963</v>
       </c>
       <c r="R8" t="n">
-        <v>7057031</v>
+        <v>7056711</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1396,53 +1361,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111940449</v>
+        <v>111941398</v>
       </c>
       <c r="B9" t="n">
-        <v>83572</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5589</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun klubbdyna</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Trichoderma nybergianum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andbrännan, Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>475958</v>
+        <v>475780</v>
       </c>
       <c r="R9" t="n">
-        <v>7056697</v>
+        <v>7056937</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1483,7 +1441,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1502,51 +1459,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111941536</v>
+        <v>111942305</v>
       </c>
       <c r="B10" t="n">
-        <v>85448</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3739</v>
+        <v>3624</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Quél.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>475722</v>
+        <v>475683</v>
       </c>
       <c r="R10" t="n">
-        <v>7056998</v>
+        <v>7057042</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1605,51 +1553,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111941398</v>
+        <v>111941536</v>
       </c>
       <c r="B11" t="n">
-        <v>93230</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>3739</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475780</v>
+        <v>475722</v>
       </c>
       <c r="R11" t="n">
-        <v>7056937</v>
+        <v>7056998</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1708,51 +1651,46 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111940665</v>
+        <v>111942167</v>
       </c>
       <c r="B12" t="n">
-        <v>85400</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1988</v>
+        <v>3739</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>475963</v>
+        <v>475832</v>
       </c>
       <c r="R12" t="n">
-        <v>7056711</v>
+        <v>7057098</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,15 +1749,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111941753</v>
+        <v>111942683</v>
       </c>
       <c r="B13" t="n">
-        <v>89114</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,35 +1760,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>475800</v>
+        <v>475748</v>
       </c>
       <c r="R13" t="n">
-        <v>7057037</v>
+        <v>7057031</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1914,51 +1847,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111940798</v>
+        <v>111941810</v>
       </c>
       <c r="B14" t="n">
-        <v>85476</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3528</v>
+        <v>4405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitterspindling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius agathosmus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Brandrud, H.Lindstr. &amp; Melot</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476006</v>
+        <v>475800</v>
       </c>
       <c r="R14" t="n">
-        <v>7056725</v>
+        <v>7057037</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2017,51 +1945,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111943231</v>
+        <v>113106102</v>
       </c>
       <c r="B15" t="n">
-        <v>73821</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>306</v>
+        <v>4412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476021</v>
+        <v>475958</v>
       </c>
       <c r="R15" t="n">
-        <v>7056723</v>
+        <v>7056698</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2102,6 +2027,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2120,15 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112818906</v>
+        <v>111940449</v>
       </c>
       <c r="B16" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85065</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2136,38 +2057,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5589</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun klubbdyna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichoderma nybergianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(T.Ulvinen &amp; H.L.Chamb.) Jaklitsch &amp; Voglmayr</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476130</v>
+        <v>475958</v>
       </c>
       <c r="R16" t="n">
-        <v>7057242</v>
+        <v>7056698</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2191,12 +2114,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2205,6 +2128,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2223,15 +2147,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112819170</v>
+        <v>111941753</v>
       </c>
       <c r="B17" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,38 +2158,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>475984</v>
+        <v>475800</v>
       </c>
       <c r="R17" t="n">
-        <v>7057183</v>
+        <v>7057037</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2294,12 +2213,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2326,54 +2245,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112819093</v>
+        <v>113715321</v>
       </c>
       <c r="B18" t="n">
-        <v>90378</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476050</v>
+        <v>475863</v>
       </c>
       <c r="R18" t="n">
-        <v>7057224</v>
+        <v>7057040</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2429,54 +2354,56 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112818753</v>
+        <v>113715305</v>
       </c>
       <c r="B19" t="n">
-        <v>90378</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andbrännan (Andbrännan), Jmt</t>
+          <t>Andbrännan, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476130</v>
+        <v>475973</v>
       </c>
       <c r="R19" t="n">
-        <v>7057242</v>
+        <v>7056769</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2529,336 +2456,6 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>113106102</v>
-      </c>
-      <c r="B20" t="n">
-        <v>86874</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>4412</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Äggvaxskivling</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hygrophorus karstenii</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Andbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>475958</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7056697</v>
-      </c>
-      <c r="S20" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>113715321</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Andbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>475863</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7057040</v>
-      </c>
-      <c r="S21" t="n">
-        <v>50</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>113715305</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Andbrännan, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>475973</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7056769</v>
-      </c>
-      <c r="S22" t="n">
-        <v>50</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37027-2023 artfynd.xlsx
+++ b/artfynd/A 37027-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818906</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112818753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112819093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111941749</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111941479</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940665</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111941398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942305</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1648,6 +1698,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111941536</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1746,6 +1801,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942167</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111942683</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1942,6 +2007,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111941810</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2043,6 +2113,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113106102</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2144,6 +2219,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940449</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111941753</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113715321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,8 +2546,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113715305</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>